--- a/TestData/TMTI0045474_VerifytheAmountiscalculatedandreflectedforNewEngagement.xlsx
+++ b/TestData/TMTI0045474_VerifytheAmountiscalculatedandreflectedforNewEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABCD804D-75ED-4F39-A8F6-3F0551C7D218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A01C7657-C0CC-4B40-817B-9A2922E0D0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="14640" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -1494,9 +1494,8 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1531,7 +1530,7 @@
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
